--- a/产品信息/联合实验室PTseq病原微生物高通量基因GenSIRO-48平台检测任务单.xlsx
+++ b/产品信息/联合实验室PTseq病原微生物高通量基因GenSIRO-48平台检测任务单.xlsx
@@ -6730,17 +6730,25 @@
       <x:c r="H7" s="177" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="I7" s="178" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="J7" s="177" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="K7" s="177" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="L7" s="178" t="s">
-        <x:v>95</x:v>
+      <x:c r="I7" s="178" t="inlineStr">
+        <x:is>
+          <x:t>◎55μL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J7" s="177" t="inlineStr">
+        <x:is>
+          <x:t>◎71μL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K7" s="177" t="inlineStr">
+        <x:is>
+          <x:t>◎103μL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L7" s="178" t="inlineStr">
+        <x:is>
+          <x:t>◎135μL</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -7044,23 +7052,35 @@
       <x:c r="D17" s="171"/>
       <x:c r="E17" s="171"/>
       <x:c r="F17" s="181"/>
-      <x:c r="G17" s="177" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="H17" s="176" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="I17" s="177" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="J17" s="177" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="K17" s="177" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="L17" s="177" t="s">
-        <x:v>153</x:v>
+      <x:c r="G17" s="177" t="inlineStr">
+        <x:is>
+          <x:t>80%乙醇（两槽各）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H17" s="176" t="inlineStr">
+        <x:is>
+          <x:t>50mL试剂槽×2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I17" s="177" t="inlineStr">
+        <x:is>
+          <x:t>◎19mL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J17" s="177" t="inlineStr">
+        <x:is>
+          <x:t>◎23mL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K17" s="177" t="inlineStr">
+        <x:is>
+          <x:t>◎31mL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L17" s="177" t="inlineStr">
+        <x:is>
+          <x:t>◎39mL</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="18" s="44" customFormat="1" ht="28">
@@ -7241,8 +7261,10 @@
       <x:c r="E24" s="184" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="F24" s="181" t="s">
-        <x:v>112</x:v>
+      <x:c r="F24" s="181" t="inlineStr">
+        <x:is>
+          <x:t>◎70μL</x:t>
+        </x:is>
       </x:c>
       <x:c r="G24" s="181" t="s">
         <x:v>174</x:v>
@@ -7279,8 +7301,10 @@
       <x:c r="E25" s="184" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="F25" s="181" t="s">
-        <x:v>179</x:v>
+      <x:c r="F25" s="181" t="inlineStr">
+        <x:is>
+          <x:t>◎6μL</x:t>
+        </x:is>
       </x:c>
       <x:c r="G25" s="181" t="s">
         <x:v>176</x:v>
@@ -7308,8 +7332,10 @@
       <x:c r="B26" s="184" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C26" s="181" t="s">
-        <x:v>181</x:v>
+      <x:c r="C26" s="181" t="inlineStr">
+        <x:is>
+          <x:t>◎40μL</x:t>
+        </x:is>
       </x:c>
       <x:c r="D26" s="181" t="s">
         <x:v>182</x:v>
@@ -7364,17 +7390,25 @@
       <x:c r="H27" s="184" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="I27" s="181" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="J27" s="181" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="K27" s="181" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="L27" s="181" t="s">
-        <x:v>186</x:v>
+      <x:c r="I27" s="181" t="inlineStr">
+        <x:is>
+          <x:t>◎6μL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J27" s="181" t="inlineStr">
+        <x:is>
+          <x:t>◎6μL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K27" s="181" t="inlineStr">
+        <x:is>
+          <x:t>◎6μL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L27" s="181" t="inlineStr">
+        <x:is>
+          <x:t>◎6μL</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="28" s="44" customFormat="1" ht="28" customHeight="1">
@@ -7691,8 +7725,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="E41" s="68"/>
-      <x:c r="F41" s="194" t="s">
-        <x:v>212</x:v>
+      <x:c r="F41" s="194" t="inlineStr">
+        <x:is>
+          <x:t>2/1</x:t>
+        </x:is>
       </x:c>
       <x:c r="G41" s="190" t="s">
         <x:v>198</x:v>
